--- a/exports/trend_1d/DATAPATTNS_full_report.xlsx
+++ b/exports/trend_1d/DATAPATTNS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>17.11</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H2" t="n">
-        <v>713.25</v>
+        <v>650.05</v>
       </c>
       <c r="I2" t="n">
         <v>659.9803719607499</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.7</v>
+        <v>-12.23</v>
       </c>
       <c r="L2" t="n">
-        <v>6.18</v>
+        <v>13.72</v>
       </c>
       <c r="M2" t="n">
-        <v>1.89</v>
+        <v>3.19</v>
       </c>
       <c r="N2" t="n">
-        <v>5.05</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>-2.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>21.06</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44628</v>
+        <v>44629</v>
       </c>
       <c r="H3" t="n">
-        <v>642.8</v>
+        <v>713.1</v>
       </c>
       <c r="I3" t="n">
         <v>690.7193424266653</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>1.12</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>9.529999999999999</v>
+        <v>10.76</v>
       </c>
       <c r="M3" t="n">
         <v>2.49</v>
       </c>
       <c r="N3" t="n">
-        <v>7.97</v>
+        <v>10.94</v>
       </c>
       <c r="O3" t="n">
         <v>-8.859999999999999</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>21.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H4" t="n">
-        <v>778</v>
+        <v>743.35</v>
       </c>
       <c r="I4" t="n">
         <v>766.3932322244844</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K4" t="n">
-        <v>9.1</v>
+        <v>4.24</v>
       </c>
       <c r="L4" t="n">
         <v>9.83</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>20.84</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44750</v>
+        <v>44753</v>
       </c>
       <c r="H5" t="n">
-        <v>708.75</v>
+        <v>731.85</v>
       </c>
       <c r="I5" t="n">
         <v>716.6726800499481</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K5" t="n">
-        <v>4.65</v>
+        <v>1.55</v>
       </c>
       <c r="L5" t="n">
         <v>6.56</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.88</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44909</v>
+        <v>44910</v>
       </c>
       <c r="H6" t="n">
-        <v>1261.75</v>
+        <v>1231.5</v>
       </c>
       <c r="I6" t="n">
         <v>1234.615464408016</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K6" t="n">
-        <v>72.41</v>
+        <v>68.27</v>
       </c>
       <c r="L6" t="n">
         <v>10.77</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.34</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44938</v>
+        <v>44939</v>
       </c>
       <c r="H7" t="n">
-        <v>1161.4</v>
+        <v>1225.75</v>
       </c>
       <c r="I7" t="n">
         <v>1221.132647224592</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>5.69</v>
+        <v>0.47</v>
       </c>
       <c r="L7" t="n">
         <v>3.29</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>14.17</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44979</v>
+        <v>44980</v>
       </c>
       <c r="H8" t="n">
-        <v>1286.75</v>
+        <v>1243.75</v>
       </c>
       <c r="I8" t="n">
         <v>1256.069624026394</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" t="n">
-        <v>4.98</v>
+        <v>1.47</v>
       </c>
       <c r="L8" t="n">
         <v>7.34</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>18.03</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H9" t="n">
-        <v>1375.7</v>
+        <v>1424.4</v>
       </c>
       <c r="I9" t="n">
         <v>1411.144022976101</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.61</v>
+        <v>-14.52</v>
       </c>
       <c r="L9" t="n">
-        <v>14.63</v>
+        <v>16.98</v>
       </c>
       <c r="M9" t="n">
         <v>0.79</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.09</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45176</v>
+        <v>45177</v>
       </c>
       <c r="H10" t="n">
-        <v>2189.45</v>
+        <v>2155.75</v>
       </c>
       <c r="I10" t="n">
         <v>2159.064958014159</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K10" t="n">
-        <v>53.71</v>
+        <v>51.34</v>
       </c>
       <c r="L10" t="n">
         <v>3.04</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>16.1</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="H11" t="n">
-        <v>1971.8</v>
+        <v>2012.7</v>
       </c>
       <c r="I11" t="n">
         <v>2007.225099994281</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K11" t="n">
-        <v>8.529999999999999</v>
+        <v>6.64</v>
       </c>
       <c r="L11" t="n">
         <v>6.5</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10.42</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45286</v>
+        <v>45287</v>
       </c>
       <c r="H12" t="n">
-        <v>1925.45</v>
+        <v>1882.9</v>
       </c>
       <c r="I12" t="n">
         <v>1888.802484970545</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.33</v>
+        <v>-6.45</v>
       </c>
       <c r="L12" t="n">
-        <v>5.54</v>
+        <v>6.67</v>
       </c>
       <c r="M12" t="n">
         <v>0.78</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="H13" t="n">
-        <v>1854.65</v>
+        <v>2019.15</v>
       </c>
       <c r="I13" t="n">
         <v>2002.592034580393</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5</v>
+        <v>-7.24</v>
       </c>
       <c r="L13" t="n">
         <v>8.869999999999999</v>
@@ -1182,7 +1337,7 @@
         <v>7.58</v>
       </c>
       <c r="N13" t="n">
-        <v>4.53</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-2.21</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>14.12</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="H14" t="n">
-        <v>2555.45</v>
+        <v>2423.85</v>
       </c>
       <c r="I14" t="n">
         <v>2474.70751323483</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>26.56</v>
+        <v>20.04</v>
       </c>
       <c r="L14" t="n">
         <v>5.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="N14" t="n">
         <v>7.75</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>23.71</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45391</v>
+        <v>45392</v>
       </c>
       <c r="H15" t="n">
-        <v>2688.3</v>
+        <v>3007</v>
       </c>
       <c r="I15" t="n">
         <v>2755.354696050819</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.91</v>
+        <v>-24.06</v>
       </c>
       <c r="L15" t="n">
-        <v>16.13</v>
+        <v>25.58</v>
       </c>
       <c r="M15" t="n">
         <v>7.27</v>
       </c>
       <c r="N15" t="n">
-        <v>8.98</v>
+        <v>11.86</v>
       </c>
       <c r="O15" t="n">
         <v>-5.15</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>21.27</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H16" t="n">
-        <v>2974.15</v>
+        <v>2617.75</v>
       </c>
       <c r="I16" t="n">
         <v>2810.586405048738</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.09</v>
+        <v>-12.94</v>
       </c>
       <c r="L16" t="n">
-        <v>12.2</v>
+        <v>20.87</v>
       </c>
       <c r="M16" t="n">
         <v>3.53</v>
       </c>
       <c r="N16" t="n">
-        <v>4.36</v>
+        <v>11.98</v>
       </c>
       <c r="O16" t="n">
         <v>11.86</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>26.09</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45477</v>
+        <v>45478</v>
       </c>
       <c r="H17" t="n">
-        <v>3179.7</v>
+        <v>3390.4</v>
       </c>
       <c r="I17" t="n">
         <v>3202.406581625357</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K17" t="n">
-        <v>-21.47</v>
+        <v>-29.52</v>
       </c>
       <c r="L17" t="n">
-        <v>23.2</v>
+        <v>39.62</v>
       </c>
       <c r="M17" t="n">
         <v>4.49</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>15.23</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H18" t="n">
-        <v>2962.9</v>
+        <v>2853.45</v>
       </c>
       <c r="I18" t="n">
         <v>2874.342397351896</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" t="n">
-        <v>-12.61</v>
+        <v>-15.84</v>
       </c>
       <c r="L18" t="n">
-        <v>14.46</v>
+        <v>16.35</v>
       </c>
       <c r="M18" t="n">
         <v>5.08</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>22.28</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="H19" t="n">
-        <v>2466.8</v>
+        <v>2503.4</v>
       </c>
       <c r="I19" t="n">
         <v>2485.850911988962</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K19" t="n">
-        <v>13.55</v>
+        <v>12.27</v>
       </c>
       <c r="L19" t="n">
         <v>8.529999999999999</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>13.27</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H20" t="n">
-        <v>2485.25</v>
+        <v>2344.8</v>
       </c>
       <c r="I20" t="n">
         <v>2376.010113254029</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.73</v>
+        <v>-6.34</v>
       </c>
       <c r="L20" t="n">
-        <v>4.93</v>
+        <v>6.81</v>
       </c>
       <c r="M20" t="n">
         <v>3.96</v>
       </c>
       <c r="N20" t="n">
-        <v>3.77</v>
+        <v>5.65</v>
       </c>
       <c r="O20" t="n">
         <v>1.48</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>15.82</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H21" t="n">
-        <v>1681.95</v>
+        <v>1878.7</v>
       </c>
       <c r="I21" t="n">
         <v>1754.972278870661</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K21" t="n">
-        <v>28.27</v>
+        <v>19.88</v>
       </c>
       <c r="L21" t="n">
         <v>7.51</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>21.38</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H22" t="n">
-        <v>2780.7</v>
+        <v>2677.4</v>
       </c>
       <c r="I22" t="n">
         <v>2709.358957863567</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K22" t="n">
-        <v>48.01</v>
+        <v>42.51</v>
       </c>
       <c r="L22" t="n">
         <v>9.800000000000001</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>12.5</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="H23" t="n">
-        <v>2711</v>
+        <v>2717.2</v>
       </c>
       <c r="I23" t="n">
         <v>2715.167114241849</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.25</v>
+        <v>-1.49</v>
       </c>
       <c r="L23" t="n">
-        <v>3.91</v>
+        <v>5.88</v>
       </c>
       <c r="M23" t="n">
         <v>1.87</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.25</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="H24" t="n">
-        <v>2896.9</v>
+        <v>2766.3</v>
       </c>
       <c r="I24" t="n">
         <v>2785.983706294311</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K24" t="n">
-        <v>6.61</v>
+        <v>1.81</v>
       </c>
       <c r="L24" t="n">
         <v>7.85</v>
@@ -1809,7 +2096,7 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>4.28</v>
+        <v>4.51</v>
       </c>
       <c r="O24" t="n">
         <v>0.23</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>14.65</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H25" t="n">
-        <v>2297.4</v>
+        <v>2610.6</v>
       </c>
       <c r="I25" t="n">
         <v>2549.72514037696</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K25" t="n">
-        <v>16.95</v>
+        <v>5.63</v>
       </c>
       <c r="L25" t="n">
         <v>5.98</v>
@@ -1866,7 +2165,7 @@
         <v>1.5</v>
       </c>
       <c r="N25" t="n">
-        <v>5.26</v>
+        <v>13.63</v>
       </c>
       <c r="O25" t="n">
         <v>-4.51</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>21.32</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="H26" t="n">
-        <v>4189.7</v>
+        <v>4142.4</v>
       </c>
       <c r="I26" t="n">
         <v>4182.900635610175</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K26" t="n">
-        <v>60.49</v>
+        <v>58.68</v>
       </c>
       <c r="L26" t="n">
         <v>11.99</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>12.08</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="H27" t="n">
-        <v>4243.9</v>
+        <v>4782.8</v>
       </c>
       <c r="I27" t="n">
         <v>4534.012283149495</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.45</v>
+        <v>-15.46</v>
       </c>
       <c r="L27" t="n">
-        <v>3.8</v>
+        <v>15.97</v>
       </c>
       <c r="M27" t="n">
-        <v>0.34</v>
+        <v>1.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6.34</v>
+        <v>12.7</v>
       </c>
       <c r="O27" t="n">
         <v>-1.13</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>19.5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H28" t="n">
-        <v>4829.2</v>
+        <v>4358.8</v>
       </c>
       <c r="I28" t="n">
         <v>4408.861952519803</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K28" t="n">
-        <v>0.97</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>14.49</v>
@@ -2037,7 +2372,7 @@
         <v>7.47</v>
       </c>
       <c r="N28" t="n">
-        <v>4.31</v>
+        <v>9.74</v>
       </c>
       <c r="O28" t="n">
         <v>12.7</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2097,6 +2444,14 @@
       <c r="Q29" t="n">
         <v>30</v>
       </c>
+      <c r="R29" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4233,7 +4588,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.8</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="6">
@@ -4243,7 +4598,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -4253,7 +4608,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8">
@@ -4263,7 +4618,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -4273,7 +4628,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -4283,7 +4638,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130.8</v>
+        <v>131.8</v>
       </c>
     </row>
     <row r="11">
@@ -4293,7 +4648,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -4303,7 +4658,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -4313,7 +4668,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.9</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="14">
@@ -4323,7 +4678,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.89</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="15">
@@ -4333,7 +4688,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.6</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="16">
@@ -4343,7 +4698,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.58</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="17">
@@ -4353,7 +4708,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>72.41</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="18">
@@ -4363,7 +4718,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="19">
@@ -4373,7 +4728,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.98</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="20">
@@ -4383,7 +4738,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.85</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -4393,7 +4748,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.2</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="22">
@@ -4403,7 +4758,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -4413,7 +4768,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -4423,7 +4778,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -4443,7 +4798,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.61</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="27">
@@ -4463,7 +4818,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
